--- a/Online Assessment 0/web_resources/Data files for Assessments/Online Assessment 0/Data3_14.xlsx
+++ b/Online Assessment 0/web_resources/Data files for Assessments/Online Assessment 0/Data3_14.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C101"/>
+  <dimension ref="A1:C51"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -362,12 +362,12 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>ReactionTime</t>
+          <t>RiskTaker?</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Happiness</t>
+          <t>IV2</t>
         </is>
       </c>
     </row>
@@ -378,10 +378,10 @@
         </is>
       </c>
       <c r="B2">
-        <v>-0.7605870231296981</v>
+        <v>-0.3428618546187733</v>
       </c>
       <c r="C2">
-        <v>2.837233178110123</v>
+        <v>0.4206605177754023</v>
       </c>
     </row>
     <row r="3">
@@ -391,10 +391,10 @@
         </is>
       </c>
       <c r="B3">
-        <v>-0.6000061957182521</v>
+        <v>-0.2597192331074642</v>
       </c>
       <c r="C3">
-        <v>-0.2468829585664501</v>
+        <v>1.370563869573672</v>
       </c>
     </row>
     <row r="4">
@@ -404,10 +404,10 @@
         </is>
       </c>
       <c r="B4">
-        <v>-2.108226948862839</v>
+        <v>-1.998153595996901</v>
       </c>
       <c r="C4">
-        <v>1.470333924257586</v>
+        <v>-1.397474506491674</v>
       </c>
     </row>
     <row r="5">
@@ -417,10 +417,10 @@
         </is>
       </c>
       <c r="B5">
-        <v>0.4251897627439961</v>
+        <v>-2.112555877904055</v>
       </c>
       <c r="C5">
-        <v>-0.07132455234384086</v>
+        <v>-0.1815508591238671</v>
       </c>
     </row>
     <row r="6">
@@ -430,10 +430,10 @@
         </is>
       </c>
       <c r="B6">
-        <v>1.047290228917968</v>
+        <v>-0.8035092764476273</v>
       </c>
       <c r="C6">
-        <v>-1.873511543679865</v>
+        <v>-1.343280091154034</v>
       </c>
     </row>
     <row r="7">
@@ -443,10 +443,10 @@
         </is>
       </c>
       <c r="B7">
-        <v>1.605424611040045</v>
+        <v>1.215204123810782</v>
       </c>
       <c r="C7">
-        <v>0.2992200438008498</v>
+        <v>0.05660093151350015</v>
       </c>
     </row>
     <row r="8">
@@ -456,10 +456,10 @@
         </is>
       </c>
       <c r="B8">
-        <v>-0.0939093097489964</v>
+        <v>-0.6444244329940173</v>
       </c>
       <c r="C8">
-        <v>1.766319740684708</v>
+        <v>0.9049757639695328</v>
       </c>
     </row>
     <row r="9">
@@ -469,10 +469,10 @@
         </is>
       </c>
       <c r="B9">
-        <v>-1.261100916489805</v>
+        <v>0.5771243752383933</v>
       </c>
       <c r="C9">
-        <v>1.083387604405395</v>
+        <v>-0.5552959327493596</v>
       </c>
     </row>
     <row r="10">
@@ -482,10 +482,10 @@
         </is>
       </c>
       <c r="B10">
-        <v>0.4282256623174455</v>
+        <v>-1.564943926780995</v>
       </c>
       <c r="C10">
-        <v>1.081247364003767</v>
+        <v>-1.319666389376185</v>
       </c>
     </row>
     <row r="11">
@@ -495,10 +495,10 @@
         </is>
       </c>
       <c r="B11">
-        <v>0.7537669136623407</v>
+        <v>0.2365220013904789</v>
       </c>
       <c r="C11">
-        <v>-0.2946955256327252</v>
+        <v>0.5243997068029328</v>
       </c>
     </row>
     <row r="12">
@@ -508,10 +508,10 @@
         </is>
       </c>
       <c r="B12">
-        <v>0.6660028116464537</v>
+        <v>0.4900718011939127</v>
       </c>
       <c r="C12">
-        <v>0.1110241684994274</v>
+        <v>0.3973717721809928</v>
       </c>
     </row>
     <row r="13">
@@ -521,10 +521,10 @@
         </is>
       </c>
       <c r="B13">
-        <v>-0.1962374080706142</v>
+        <v>-1.630225234550812</v>
       </c>
       <c r="C13">
-        <v>-0.0740448284238721</v>
+        <v>-1.854731850929402</v>
       </c>
     </row>
     <row r="14">
@@ -534,10 +534,10 @@
         </is>
       </c>
       <c r="B14">
-        <v>-0.91430727810247</v>
+        <v>0.002146516005236159</v>
       </c>
       <c r="C14">
-        <v>-0.1349789480135121</v>
+        <v>-2.078425871680064</v>
       </c>
     </row>
     <row r="15">
@@ -547,10 +547,10 @@
         </is>
       </c>
       <c r="B15">
-        <v>0.6066177639363984</v>
+        <v>-0.9035967705422433</v>
       </c>
       <c r="C15">
-        <v>1.325454498078402</v>
+        <v>0.1524164677736758</v>
       </c>
     </row>
     <row r="16">
@@ -560,10 +560,10 @@
         </is>
       </c>
       <c r="B16">
-        <v>-0.5355928885810158</v>
+        <v>-0.2205565762125057</v>
       </c>
       <c r="C16">
-        <v>0.4074023961864517</v>
+        <v>0.1407361012124091</v>
       </c>
     </row>
     <row r="17">
@@ -573,10 +573,10 @@
         </is>
       </c>
       <c r="B17">
-        <v>0.7386979407121346</v>
+        <v>1.134866665502878</v>
       </c>
       <c r="C17">
-        <v>-1.699606901217404</v>
+        <v>-0.06329846551893603</v>
       </c>
     </row>
     <row r="18">
@@ -586,10 +586,10 @@
         </is>
       </c>
       <c r="B18">
-        <v>2.002664641076592</v>
+        <v>1.038074582821265</v>
       </c>
       <c r="C18">
-        <v>-1.736466688245987</v>
+        <v>-1.718488993424617</v>
       </c>
     </row>
     <row r="19">
@@ -599,10 +599,10 @@
         </is>
       </c>
       <c r="B19">
-        <v>0.7095054024458353</v>
+        <v>0.702834526705635</v>
       </c>
       <c r="C19">
-        <v>0.0005414519514085336</v>
+        <v>0.08593561139999201</v>
       </c>
     </row>
     <row r="20">
@@ -612,10 +612,10 @@
         </is>
       </c>
       <c r="B20">
-        <v>-0.1104780178811444</v>
+        <v>1.560301855717546</v>
       </c>
       <c r="C20">
-        <v>-0.01839718885500274</v>
+        <v>0.4742060596187492</v>
       </c>
     </row>
     <row r="21">
@@ -625,10 +625,10 @@
         </is>
       </c>
       <c r="B21">
-        <v>-0.3075945403172036</v>
+        <v>0.03165707523543226</v>
       </c>
       <c r="C21">
-        <v>-0.2737169367559309</v>
+        <v>1.138535099199046</v>
       </c>
     </row>
     <row r="22">
@@ -638,10 +638,10 @@
         </is>
       </c>
       <c r="B22">
-        <v>0.1001032881962206</v>
+        <v>-0.09689358256019129</v>
       </c>
       <c r="C22">
-        <v>0.7366429632282419</v>
+        <v>0.1021756018367016</v>
       </c>
     </row>
     <row r="23">
@@ -651,10 +651,10 @@
         </is>
       </c>
       <c r="B23">
-        <v>0.8239637725285778</v>
+        <v>0.9811915192822754</v>
       </c>
       <c r="C23">
-        <v>1.300013827793995</v>
+        <v>2.304951685285652</v>
       </c>
     </row>
     <row r="24">
@@ -664,10 +664,10 @@
         </is>
       </c>
       <c r="B24">
-        <v>0.451524120380308</v>
+        <v>1.318812723121606</v>
       </c>
       <c r="C24">
-        <v>0.2013358691723663</v>
+        <v>1.179828686709643</v>
       </c>
     </row>
     <row r="25">
@@ -677,10 +677,10 @@
         </is>
       </c>
       <c r="B25">
-        <v>0.7783186779514784</v>
+        <v>-0.02355098707514709</v>
       </c>
       <c r="C25">
-        <v>0.1598223649128369</v>
+        <v>-0.489126561737071</v>
       </c>
     </row>
     <row r="26">
@@ -690,10 +690,10 @@
         </is>
       </c>
       <c r="B26">
-        <v>1.45995284010386</v>
+        <v>0.690246968053153</v>
       </c>
       <c r="C26">
-        <v>-1.27419210981524</v>
+        <v>0.7789810947335096</v>
       </c>
     </row>
     <row r="27">
@@ -703,10 +703,10 @@
         </is>
       </c>
       <c r="B27">
-        <v>-1.083272694254476</v>
+        <v>0.216655090725787</v>
       </c>
       <c r="C27">
-        <v>-0.7473923812496904</v>
+        <v>0.7431674367568269</v>
       </c>
     </row>
     <row r="28">
@@ -716,10 +716,10 @@
         </is>
       </c>
       <c r="B28">
-        <v>-0.2439930216275334</v>
+        <v>1.352893495331407</v>
       </c>
       <c r="C28">
-        <v>-0.695130547914064</v>
+        <v>1.05547610839765</v>
       </c>
     </row>
     <row r="29">
@@ -729,10 +729,10 @@
         </is>
       </c>
       <c r="B29">
-        <v>2.046957185568297</v>
+        <v>-0.4698473996870031</v>
       </c>
       <c r="C29">
-        <v>-1.299575337143235</v>
+        <v>-0.4169886056295958</v>
       </c>
     </row>
     <row r="30">
@@ -742,10 +742,10 @@
         </is>
       </c>
       <c r="B30">
-        <v>-0.4824675990905894</v>
+        <v>-0.3391122366592544</v>
       </c>
       <c r="C30">
-        <v>0.6629662715261866</v>
+        <v>0.3290475512115514</v>
       </c>
     </row>
     <row r="31">
@@ -755,10 +755,10 @@
         </is>
       </c>
       <c r="B31">
-        <v>-0.5199798586887006</v>
+        <v>-0.5246915269779757</v>
       </c>
       <c r="C31">
-        <v>-1.772825369166713</v>
+        <v>0.2964131486344493</v>
       </c>
     </row>
     <row r="32">
@@ -768,10 +768,10 @@
         </is>
       </c>
       <c r="B32">
-        <v>0.779414845046711</v>
+        <v>-0.02547078331624878</v>
       </c>
       <c r="C32">
-        <v>0.6944480825181385</v>
+        <v>1.390329591486145</v>
       </c>
     </row>
     <row r="33">
@@ -781,10 +781,10 @@
         </is>
       </c>
       <c r="B33">
-        <v>1.149397365429881</v>
+        <v>-0.9312909943522282</v>
       </c>
       <c r="C33">
-        <v>-0.6809972661778819</v>
+        <v>-0.6812398451795896</v>
       </c>
     </row>
     <row r="34">
@@ -794,10 +794,10 @@
         </is>
       </c>
       <c r="B34">
-        <v>-0.08767403954165001</v>
+        <v>1.164355506169845</v>
       </c>
       <c r="C34">
-        <v>0.6472257990573869</v>
+        <v>1.176077618857707</v>
       </c>
     </row>
     <row r="35">
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="B35">
-        <v>-0.9373418689388746</v>
+        <v>-1.193551262315287</v>
       </c>
       <c r="C35">
-        <v>1.256585629815324</v>
+        <v>-0.05838414196501918</v>
       </c>
     </row>
     <row r="36">
@@ -820,10 +820,10 @@
         </is>
       </c>
       <c r="B36">
-        <v>-0.6311107568124977</v>
+        <v>1.196834767837846</v>
       </c>
       <c r="C36">
-        <v>0.0362393366490962</v>
+        <v>0.7516850736724305</v>
       </c>
     </row>
     <row r="37">
@@ -833,10 +833,10 @@
         </is>
       </c>
       <c r="B37">
-        <v>0.983261244831545</v>
+        <v>-1.07685326405372</v>
       </c>
       <c r="C37">
-        <v>-2.997233051544878</v>
+        <v>-0.3526317030842039</v>
       </c>
     </row>
     <row r="38">
@@ -846,10 +846,10 @@
         </is>
       </c>
       <c r="B38">
-        <v>-0.2334713924351373</v>
+        <v>1.687286641624895</v>
       </c>
       <c r="C38">
-        <v>0.03716602571945688</v>
+        <v>1.085367861632044</v>
       </c>
     </row>
     <row r="39">
@@ -859,10 +859,10 @@
         </is>
       </c>
       <c r="B39">
-        <v>-0.8073357787844115</v>
+        <v>-1.550393640966552</v>
       </c>
       <c r="C39">
-        <v>0.9862111588101103</v>
+        <v>-0.7323446413455809</v>
       </c>
     </row>
     <row r="40">
@@ -872,10 +872,10 @@
         </is>
       </c>
       <c r="B40">
-        <v>0.2934111790557812</v>
+        <v>0.9983385082063004</v>
       </c>
       <c r="C40">
-        <v>0.1049399746780415</v>
+        <v>0.9598183053175495</v>
       </c>
     </row>
     <row r="41">
@@ -885,10 +885,10 @@
         </is>
       </c>
       <c r="B41">
-        <v>-0.9484481773173296</v>
+        <v>2.114839616210701</v>
       </c>
       <c r="C41">
-        <v>0.2238361795566765</v>
+        <v>1.939047302907787</v>
       </c>
     </row>
     <row r="42">
@@ -898,10 +898,10 @@
         </is>
       </c>
       <c r="B42">
-        <v>-0.03294180165533458</v>
+        <v>0.9978525245696477</v>
       </c>
       <c r="C42">
-        <v>0.329084687126427</v>
+        <v>1.830915990441932</v>
       </c>
     </row>
     <row r="43">
@@ -911,10 +911,10 @@
         </is>
       </c>
       <c r="B43">
-        <v>-0.02494144259991833</v>
+        <v>-0.3640451742510147</v>
       </c>
       <c r="C43">
-        <v>-1.346138488662458</v>
+        <v>0.6239540926222598</v>
       </c>
     </row>
     <row r="44">
@@ -924,10 +924,10 @@
         </is>
       </c>
       <c r="B44">
-        <v>1.308454429340932</v>
+        <v>-1.208823327855792</v>
       </c>
       <c r="C44">
-        <v>0.5072442909914485</v>
+        <v>0.01679540387970763</v>
       </c>
     </row>
     <row r="45">
@@ -937,10 +937,10 @@
         </is>
       </c>
       <c r="B45">
-        <v>0.08898739285961312</v>
+        <v>-1.27533043274827</v>
       </c>
       <c r="C45">
-        <v>-1.48603975227622</v>
+        <v>-0.1242387291009426</v>
       </c>
     </row>
     <row r="46">
@@ -950,10 +950,10 @@
         </is>
       </c>
       <c r="B46">
-        <v>0.06143105294665535</v>
+        <v>1.60903557306611</v>
       </c>
       <c r="C46">
-        <v>-0.6007026288229761</v>
+        <v>1.556532993161804</v>
       </c>
     </row>
     <row r="47">
@@ -963,10 +963,10 @@
         </is>
       </c>
       <c r="B47">
-        <v>-1.040392963970203</v>
+        <v>-2.529518699022768</v>
       </c>
       <c r="C47">
-        <v>0.4497741218931415</v>
+        <v>-0.7915322306005298</v>
       </c>
     </row>
     <row r="48">
@@ -976,10 +976,10 @@
         </is>
       </c>
       <c r="B48">
-        <v>0.4335960649460849</v>
+        <v>-1.21840125905009</v>
       </c>
       <c r="C48">
-        <v>-0.03156447158907047</v>
+        <v>0.5267051861691607</v>
       </c>
     </row>
     <row r="49">
@@ -989,10 +989,10 @@
         </is>
       </c>
       <c r="B49">
-        <v>-0.04073969816329321</v>
+        <v>-0.5267362452712763</v>
       </c>
       <c r="C49">
-        <v>0.9025103927155493</v>
+        <v>0.457468814114076</v>
       </c>
     </row>
     <row r="50">
@@ -1002,10 +1002,10 @@
         </is>
       </c>
       <c r="B50">
-        <v>-0.08872332774542549</v>
+        <v>-0.05472956530514378</v>
       </c>
       <c r="C50">
-        <v>1.020849411827048</v>
+        <v>-0.2494451001068026</v>
       </c>
     </row>
     <row r="51">
@@ -1015,660 +1015,10 @@
         </is>
       </c>
       <c r="B51">
-        <v>-0.6601610248411929</v>
+        <v>-1.260001721588382</v>
       </c>
       <c r="C51">
-        <v>-0.4167993100307924</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>51</t>
-        </is>
-      </c>
-      <c r="B52">
-        <v>-1.302554263860878</v>
-      </c>
-      <c r="C52">
-        <v>1.431804476997018</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>52</t>
-        </is>
-      </c>
-      <c r="B53">
-        <v>-0.4239192247361361</v>
-      </c>
-      <c r="C53">
-        <v>0.5695798647269212</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>53</t>
-        </is>
-      </c>
-      <c r="B54">
-        <v>-1.096511363759635</v>
-      </c>
-      <c r="C54">
-        <v>-0.4350354863432843</v>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>54</t>
-        </is>
-      </c>
-      <c r="B55">
-        <v>-0.886778924956482</v>
-      </c>
-      <c r="C55">
-        <v>0.6961550513842644</v>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>55</t>
-        </is>
-      </c>
-      <c r="B56">
-        <v>0.1252858706141248</v>
-      </c>
-      <c r="C56">
-        <v>0.4290326658509964</v>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>56</t>
-        </is>
-      </c>
-      <c r="B57">
-        <v>-0.3162070824153957</v>
-      </c>
-      <c r="C57">
-        <v>-1.006238078273896</v>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>57</t>
-        </is>
-      </c>
-      <c r="B58">
-        <v>-0.675606487864672</v>
-      </c>
-      <c r="C58">
-        <v>0.1325015521989983</v>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>58</t>
-        </is>
-      </c>
-      <c r="B59">
-        <v>1.337205717017445</v>
-      </c>
-      <c r="C59">
-        <v>-0.5814851200560571</v>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>59</t>
-        </is>
-      </c>
-      <c r="B60">
-        <v>0.836536801333236</v>
-      </c>
-      <c r="C60">
-        <v>-1.925536973277122</v>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="B61">
-        <v>0.8749949290911589</v>
-      </c>
-      <c r="C61">
-        <v>-1.642263277168988</v>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>61</t>
-        </is>
-      </c>
-      <c r="B62">
-        <v>1.816225309905721</v>
-      </c>
-      <c r="C62">
-        <v>-0.3979169264346128</v>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>62</t>
-        </is>
-      </c>
-      <c r="B63">
-        <v>2.28515614475157</v>
-      </c>
-      <c r="C63">
-        <v>-0.7442925747889916</v>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>63</t>
-        </is>
-      </c>
-      <c r="B64">
-        <v>-0.650356448511498</v>
-      </c>
-      <c r="C64">
-        <v>1.505132979043695</v>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>64</t>
-        </is>
-      </c>
-      <c r="B65">
-        <v>-0.4439375557470848</v>
-      </c>
-      <c r="C65">
-        <v>-0.8850085565410617</v>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="inlineStr">
-        <is>
-          <t>65</t>
-        </is>
-      </c>
-      <c r="B66">
-        <v>0.7486981706421575</v>
-      </c>
-      <c r="C66">
-        <v>-0.6533626638438441</v>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t>66</t>
-        </is>
-      </c>
-      <c r="B67">
-        <v>1.313405741660754</v>
-      </c>
-      <c r="C67">
-        <v>-0.898900685204971</v>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="inlineStr">
-        <is>
-          <t>67</t>
-        </is>
-      </c>
-      <c r="B68">
-        <v>-0.5691339760407295</v>
-      </c>
-      <c r="C68">
-        <v>0.4061092946585738</v>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="inlineStr">
-        <is>
-          <t>68</t>
-        </is>
-      </c>
-      <c r="B69">
-        <v>-0.4393963252387649</v>
-      </c>
-      <c r="C69">
-        <v>0.5058850380968605</v>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="inlineStr">
-        <is>
-          <t>69</t>
-        </is>
-      </c>
-      <c r="B70">
-        <v>-0.006671339387223053</v>
-      </c>
-      <c r="C70">
-        <v>0.5012369250825103</v>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="B71">
-        <v>-2.41194344934663</v>
-      </c>
-      <c r="C71">
-        <v>0.4016909836651288</v>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="inlineStr">
-        <is>
-          <t>71</t>
-        </is>
-      </c>
-      <c r="B72">
-        <v>-0.3955972034609504</v>
-      </c>
-      <c r="C72">
-        <v>-0.3466623874844134</v>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="inlineStr">
-        <is>
-          <t>72</t>
-        </is>
-      </c>
-      <c r="B73">
-        <v>-0.1920723322238588</v>
-      </c>
-      <c r="C73">
-        <v>0.4423378060240304</v>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="inlineStr">
-        <is>
-          <t>73</t>
-        </is>
-      </c>
-      <c r="B74">
-        <v>-0.6061474921104251</v>
-      </c>
-      <c r="C74">
-        <v>-0.5076066554920553</v>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="inlineStr">
-        <is>
-          <t>74</t>
-        </is>
-      </c>
-      <c r="B75">
-        <v>0.05733371251948743</v>
-      </c>
-      <c r="C75">
-        <v>-1.405643240255094</v>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="inlineStr">
-        <is>
-          <t>75</t>
-        </is>
-      </c>
-      <c r="B76">
-        <v>2.616416785506531</v>
-      </c>
-      <c r="C76">
-        <v>-0.1709551292239112</v>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="inlineStr">
-        <is>
-          <t>76</t>
-        </is>
-      </c>
-      <c r="B77">
-        <v>-1.598358924319169</v>
-      </c>
-      <c r="C77">
-        <v>-1.249278070144744</v>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="inlineStr">
-        <is>
-          <t>77</t>
-        </is>
-      </c>
-      <c r="B78">
-        <v>0.4803490948106151</v>
-      </c>
-      <c r="C78">
-        <v>0.242471594701813</v>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="inlineStr">
-        <is>
-          <t>78</t>
-        </is>
-      </c>
-      <c r="B79">
-        <v>0.1761267677527755</v>
-      </c>
-      <c r="C79">
-        <v>1.589089966803877</v>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="inlineStr">
-        <is>
-          <t>79</t>
-        </is>
-      </c>
-      <c r="B80">
-        <v>-0.197399282076038</v>
-      </c>
-      <c r="C80">
-        <v>0.2071382084910871</v>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
-      <c r="B81">
-        <v>-0.3103752772854193</v>
-      </c>
-      <c r="C81">
-        <v>1.144671554195406</v>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="inlineStr">
-        <is>
-          <t>81</t>
-        </is>
-      </c>
-      <c r="B82">
-        <v>0.6542595546560974</v>
-      </c>
-      <c r="C82">
-        <v>-0.963815093654329</v>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="inlineStr">
-        <is>
-          <t>82</t>
-        </is>
-      </c>
-      <c r="B83">
-        <v>-1.176314741468259</v>
-      </c>
-      <c r="C83">
-        <v>-0.7712907325273736</v>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" t="inlineStr">
-        <is>
-          <t>83</t>
-        </is>
-      </c>
-      <c r="B84">
-        <v>0.5467048223454812</v>
-      </c>
-      <c r="C84">
-        <v>1.084381572677494</v>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="inlineStr">
-        <is>
-          <t>84</t>
-        </is>
-      </c>
-      <c r="B85">
-        <v>-1.317202569612257</v>
-      </c>
-      <c r="C85">
-        <v>2.543374271908475</v>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="inlineStr">
-        <is>
-          <t>85</t>
-        </is>
-      </c>
-      <c r="B86">
-        <v>0.6419950167933419</v>
-      </c>
-      <c r="C86">
-        <v>-3.02973663786521</v>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="inlineStr">
-        <is>
-          <t>86</t>
-        </is>
-      </c>
-      <c r="B87">
-        <v>1.193071642165633</v>
-      </c>
-      <c r="C87">
-        <v>-2.466788943678339</v>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="inlineStr">
-        <is>
-          <t>87</t>
-        </is>
-      </c>
-      <c r="B88">
-        <v>-0.6740403692561694</v>
-      </c>
-      <c r="C88">
-        <v>0.9448094944448064</v>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="inlineStr">
-        <is>
-          <t>88</t>
-        </is>
-      </c>
-      <c r="B89">
-        <v>1.08400841943163</v>
-      </c>
-      <c r="C89">
-        <v>0.05811067323562014</v>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" t="inlineStr">
-        <is>
-          <t>89</t>
-        </is>
-      </c>
-      <c r="B90">
-        <v>-1.269307281146068</v>
-      </c>
-      <c r="C90">
-        <v>0.7543650178524772</v>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" t="inlineStr">
-        <is>
-          <t>90</t>
-        </is>
-      </c>
-      <c r="B91">
-        <v>0.5726384250035527</v>
-      </c>
-      <c r="C91">
-        <v>-1.688345523388026</v>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" t="inlineStr">
-        <is>
-          <t>91</t>
-        </is>
-      </c>
-      <c r="B92">
-        <v>-0.5000281178968683</v>
-      </c>
-      <c r="C92">
-        <v>0.6593469611000414</v>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" t="inlineStr">
-        <is>
-          <t>92</t>
-        </is>
-      </c>
-      <c r="B93">
-        <v>0.3296523710272858</v>
-      </c>
-      <c r="C93">
-        <v>-0.6976439567436749</v>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" t="inlineStr">
-        <is>
-          <t>93</t>
-        </is>
-      </c>
-      <c r="B94">
-        <v>-1.423079056179629</v>
-      </c>
-      <c r="C94">
-        <v>0.5992775352552401</v>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" t="inlineStr">
-        <is>
-          <t>94</t>
-        </is>
-      </c>
-      <c r="B95">
-        <v>0.7171339896397466</v>
-      </c>
-      <c r="C95">
-        <v>-0.007347013696306914</v>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" t="inlineStr">
-        <is>
-          <t>95</t>
-        </is>
-      </c>
-      <c r="B96">
-        <v>0.1701876438432829</v>
-      </c>
-      <c r="C96">
-        <v>-1.152949512708491</v>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" t="inlineStr">
-        <is>
-          <t>96</t>
-        </is>
-      </c>
-      <c r="B97">
-        <v>-0.6818821221252243</v>
-      </c>
-      <c r="C97">
-        <v>-0.7163697054481932</v>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" t="inlineStr">
-        <is>
-          <t>97</t>
-        </is>
-      </c>
-      <c r="B98">
-        <v>0.8766134386564038</v>
-      </c>
-      <c r="C98">
-        <v>0.2105216595319067</v>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" t="inlineStr">
-        <is>
-          <t>98</t>
-        </is>
-      </c>
-      <c r="B99">
-        <v>-1.000924194275312</v>
-      </c>
-      <c r="C99">
-        <v>1.811225047743316</v>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" t="inlineStr">
-        <is>
-          <t>99</t>
-        </is>
-      </c>
-      <c r="B100">
-        <v>0.8639771353831039</v>
-      </c>
-      <c r="C100">
-        <v>0.9609468297388313</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="B101">
-        <v>-0.09188694877679188</v>
-      </c>
-      <c r="C101">
-        <v>-0.8743980946178137</v>
+        <v>-1.394024407159559</v>
       </c>
     </row>
   </sheetData>
